--- a/file/table/TSIG_LidarDensidadNodos.xlsx
+++ b/file/table/TSIG_LidarDensidadNodos.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29902"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pruebacorreoescuelaingeduco-my.sharepoint.com/personal/william_aguilar_escuelaing_edu_co/Documents/UECIJG.ClassSourcecode/TSIG/Taller6/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.TSIG\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{AAFADE56-D42E-473E-8E40-8A534ED589F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A781B62-D39F-4D05-A4FC-EB80A1880A43}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58CF731F-F54A-4607-B260-4CE97B87467A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{45CD01C3-35BE-4EE0-8D5A-358151A4FF06}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Lidar" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,38 +36,57 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>P</t>
-  </si>
-  <si>
-    <t>d</t>
-  </si>
-  <si>
-    <t>CX</t>
-  </si>
-  <si>
-    <t>CY</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
   <si>
     <t>Higher right</t>
   </si>
   <si>
     <t>Lower left</t>
+  </si>
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>Points, pts</t>
+  </si>
+  <si>
+    <t>Layer extent</t>
+  </si>
+  <si>
+    <t>Calculations</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>CX (m)</t>
+  </si>
+  <si>
+    <t>CY (m)</t>
+  </si>
+  <si>
+    <t>Distance (m)</t>
+  </si>
+  <si>
+    <t>Area, A (m²)</t>
+  </si>
+  <si>
+    <t>Area (ha)</t>
+  </si>
+  <si>
+    <t>Density, A/pts (m²/pt)</t>
+  </si>
+  <si>
+    <t>Separation (m)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0000000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -90,15 +109,21 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -106,16 +131,163 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -450,89 +622,129 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F21A86B9-88D5-40C6-BE20-B5C00DD2F0A4}">
-  <dimension ref="B2:D9"/>
+  <dimension ref="B2:D14"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="2.59765625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.9296875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="15.86328125" style="1" customWidth="1"/>
     <col min="4" max="4" width="19.9296875" style="1" customWidth="1"/>
     <col min="5" max="16384" width="9.06640625" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.6">
-      <c r="C2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>5</v>
-      </c>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.6">
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3">
+      <c r="D3" s="13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.6">
+      <c r="B4" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3">
         <v>617200</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D4" s="5">
         <v>3356200</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.6">
-      <c r="B4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="3">
-        <v>617699.98999999894</v>
-      </c>
-      <c r="D4" s="3">
-        <v>3356799.99</v>
-      </c>
-    </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.6">
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="2">
-        <f>ABS(C3-C4)</f>
-        <v>499.98999999894295</v>
-      </c>
-      <c r="D5" s="2">
-        <f>ABS(D3-D4)</f>
-        <v>599.99000000022352</v>
+      <c r="C5" s="3">
+        <v>617700</v>
+      </c>
+      <c r="D5" s="5">
+        <v>3356800</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.6">
-      <c r="B6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="1">
-        <f>C5*D5</f>
-        <v>299989.00009947753</v>
+      <c r="B6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="7">
+        <f>ABS(C4-C5)</f>
+        <v>500</v>
+      </c>
+      <c r="D6" s="8">
+        <f>ABS(D4-D5)</f>
+        <v>600</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.6">
-      <c r="B7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" s="4">
-        <v>4344514</v>
-      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.6">
       <c r="B8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.6">
+      <c r="B9" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.6">
+      <c r="B10" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="15">
+        <f>C6*D6</f>
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.6">
+      <c r="B11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="15">
+        <f>C10/10000</f>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.6">
+      <c r="B12" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="1">
-        <f>C6/C7</f>
-        <v>6.9050070985955517E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.6">
-      <c r="C9" s="1">
-        <f>C8^0.5</f>
-        <v>0.2627738019399109</v>
+      <c r="C12" s="10">
+        <v>4344514</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.6">
+      <c r="B13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="9">
+        <f>C10/C12</f>
+        <v>6.9052602891830933E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.6">
+      <c r="B14" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="16">
+        <f>C13^0.5</f>
+        <v>0.26277861954852971</v>
       </c>
     </row>
   </sheetData>
